--- a/data/trans_camb/P16A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,55</t>
+          <t>-0,62; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,44</t>
+          <t>-1,09; 0,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,43</t>
+          <t>-0,92; 1,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,23</t>
+          <t>-4,17; 0,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,21</t>
+          <t>-3,61; 1,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,06</t>
+          <t>-4,57; 1,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,43</t>
+          <t>-2,08; 0,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,59</t>
+          <t>-2,08; 0,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,78</t>
+          <t>-2,43; 0,75</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,39; 14,27</t>
+          <t>-78,86; 20,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 49,44</t>
+          <t>-67,55; 53,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,95; 95,52</t>
+          <t>-94,63; 65,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 31,39</t>
+          <t>-68,81; 35,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,04; 44,82</t>
+          <t>-69,0; 29,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-84,18; 70,5</t>
+          <t>-87,03; 74,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,84</t>
+          <t>-0,46; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,31</t>
+          <t>-0,73; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,12</t>
+          <t>-1,15; 0,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,55</t>
+          <t>-1,73; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,26</t>
+          <t>-4,07; 0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,72</t>
+          <t>-4,48; 0,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,21</t>
+          <t>-0,49; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,47</t>
+          <t>-1,86; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,49</t>
+          <t>-2,08; 0,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 585,97</t>
+          <t>-49,34; 529,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 376,54</t>
+          <t>-66,06; 352,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-95,68; 1053,69</t>
+          <t>-97,47; 845,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 104,41</t>
+          <t>-30,78; 99,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 10,3</t>
+          <t>-70,81; 3,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 25,88</t>
+          <t>-75,84; 20,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 118,21</t>
+          <t>-18,66; 99,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 28,3</t>
+          <t>-60,17; 22,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 27,9</t>
+          <t>-68,28; 30,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,21</t>
+          <t>-2,9; -0,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,33</t>
+          <t>-3,06; -0,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,57</t>
+          <t>-2,41; 0,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,08</t>
+          <t>0,32; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,87</t>
+          <t>-1,17; 3,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,07</t>
+          <t>-2,27; 1,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,91</t>
+          <t>-0,72; 1,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,88</t>
+          <t>-1,61; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,44</t>
+          <t>-1,9; 0,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,59; 9,67</t>
+          <t>-90,23; 9,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,71; 3,62</t>
+          <t>-93,49; -18,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 58,81</t>
+          <t>-81,93; 52,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 211,29</t>
+          <t>4,56; 205,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 126,67</t>
+          <t>-28,74; 133,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 50,08</t>
+          <t>-54,9; 53,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 94,91</t>
+          <t>-22,32; 83,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 41,7</t>
+          <t>-49,71; 41,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 21,98</t>
+          <t>-56,27; 25,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,44</t>
+          <t>-2,45; 0,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,66</t>
+          <t>-2,3; 0,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,49</t>
+          <t>-2,12; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,0</t>
+          <t>-2,24; 2,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,27</t>
+          <t>-2,3; 2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,0</t>
+          <t>-1,36; 3,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,34</t>
+          <t>-1,71; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,96</t>
+          <t>-1,87; 0,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,56</t>
+          <t>-1,5; 1,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,7; 79,23</t>
+          <t>-88,93; 75,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 104,73</t>
+          <t>-84,14; 114,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 149,93</t>
+          <t>-75,78; 137,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 100,27</t>
+          <t>-41,99; 107,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 85,21</t>
+          <t>-46,02; 89,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 113,16</t>
+          <t>-27,31; 108,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 62,05</t>
+          <t>-47,78; 65,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 47,74</t>
+          <t>-49,73; 43,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 69,34</t>
+          <t>-39,58; 73,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,71</t>
+          <t>-5,17; -0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,56</t>
+          <t>-4,27; 0,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,67</t>
+          <t>-1,81; 2,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,46</t>
+          <t>-4,05; 2,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,14</t>
+          <t>-5,81; 0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,1</t>
+          <t>-2,95; 2,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,26</t>
+          <t>-3,76; 0,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -0,49</t>
+          <t>-4,32; -0,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,12</t>
+          <t>-1,8; 2,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,05</t>
+          <t>-95,4; -19,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 45,71</t>
+          <t>-86,99; 72,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 152,06</t>
+          <t>-41,52; 160,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 51,55</t>
+          <t>-47,83; 53,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 7,16</t>
+          <t>-65,97; 15,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 64,99</t>
+          <t>-33,51; 63,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 9,39</t>
+          <t>-59,26; 7,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-68,85; -9,31</t>
+          <t>-69,08; -10,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 54,65</t>
+          <t>-27,14; 59,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,37</t>
+          <t>-4,35; 2,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,6</t>
+          <t>-5,38; 0,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,6</t>
+          <t>-4,2; 1,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 1,66</t>
+          <t>-7,26; 2,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -1,03</t>
+          <t>-9,16; -0,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -2,82</t>
+          <t>-11,54; -2,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,38</t>
+          <t>-4,93; 1,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -1,05</t>
+          <t>-6,36; -1,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -1,46</t>
+          <t>-6,94; -1,45</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 110,87</t>
+          <t>-69,64; 110,2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,36; 51,74</t>
+          <t>-84,17; 31,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,22; 68,16</t>
+          <t>-65,04; 75,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 19,46</t>
+          <t>-55,83; 26,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -8,14</t>
+          <t>-67,1; -8,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,8; -29,56</t>
+          <t>-84,55; -30,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 23,4</t>
+          <t>-51,73; 20,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,64; -14,58</t>
+          <t>-66,84; -18,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,05; -23,02</t>
+          <t>-74,12; -23,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 0,05</t>
+          <t>-10,01; 0,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,1</t>
+          <t>-9,11; 0,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,82</t>
+          <t>-9,96; -0,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,75</t>
+          <t>0,64; 9,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,28</t>
+          <t>-5,06; 3,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,56</t>
+          <t>-0,16; 7,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,6</t>
+          <t>-2,1; 4,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,05</t>
+          <t>-5,02; 1,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,89</t>
+          <t>-2,58; 3,3</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 20,42</t>
+          <t>-87,74; 17,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 5,37</t>
+          <t>-76,08; 27,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,36; -9,28</t>
+          <t>-78,05; -6,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,14; 201,81</t>
+          <t>4,15; 194,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 73,41</t>
+          <t>-54,37; 65,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 154,85</t>
+          <t>-2,92; 150,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 81,4</t>
+          <t>-23,22; 77,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 18,89</t>
+          <t>-52,99; 20,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 49,35</t>
+          <t>-26,0; 59,57</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,23</t>
+          <t>-1,58; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,32</t>
+          <t>-1,61; -0,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,5</t>
+          <t>-1,1; 0,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,81</t>
+          <t>-0,47; 1,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,04</t>
+          <t>-2,36; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,65</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,58</t>
+          <t>-0,72; 0,67</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,46</t>
+          <t>-1,65; -0,43</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,37</t>
+          <t>-0,96; 0,38</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -11,67</t>
+          <t>-61,17; -12,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -16,92</t>
+          <t>-60,5; -15,87</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 27,09</t>
+          <t>-40,54; 22,73</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 37,79</t>
+          <t>-8,14; 37,26</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 0,45</t>
+          <t>-40,08; -3,02</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 13,09</t>
+          <t>-26,33; 13,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 17,27</t>
+          <t>-17,38; 19,7</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -12,68</t>
+          <t>-39,86; -12,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 10,85</t>
+          <t>-23,47; 11,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,53</t>
+          <t>-0,55; 1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,44</t>
+          <t>-1,12; 0,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,46</t>
+          <t>-0,91; 1,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,37</t>
+          <t>-4,26; 0,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,21</t>
+          <t>-3,54; 1,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,54</t>
+          <t>-4,24; 2,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,43</t>
+          <t>-2,05; 0,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,43</t>
+          <t>-2,01; 0,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,75</t>
+          <t>-2,45; 0,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>-26,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-47,4%</t>
+          <t>-40,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-47,28%</t>
+          <t>-40,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 20,24</t>
+          <t>-78,31; 19,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 53,21</t>
+          <t>-69,41; 39,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,63; 65,0</t>
+          <t>-83,13; 87,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,81; 35,14</t>
+          <t>-69,65; 42,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 29,21</t>
+          <t>-66,68; 34,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 74,43</t>
+          <t>-85,58; 49,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,98</t>
+          <t>-0,48; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,29</t>
+          <t>-0,65; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,92</t>
+          <t>-0,68; 2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,28</t>
+          <t>-1,68; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,05</t>
+          <t>-4,03; 0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,73</t>
+          <t>-3,65; 0,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,11</t>
+          <t>-0,4; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,41</t>
+          <t>-1,84; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,51</t>
+          <t>-1,69; 1,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-40,97%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-41,33%</t>
+          <t>-32,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,47%</t>
+          <t>-13,47%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 529,18</t>
+          <t>-58,34; 580,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 352,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,47; 845,18</t>
+          <t>-100,0; 805,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 99,15</t>
+          <t>-29,77; 108,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 3,28</t>
+          <t>-71,45; 3,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,84; 20,56</t>
+          <t>-68,43; 24,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 99,47</t>
+          <t>-14,32; 110,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 22,31</t>
+          <t>-57,85; 22,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 30,2</t>
+          <t>-53,33; 63,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,12</t>
+          <t>-2,95; -0,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,39</t>
+          <t>-3,09; -0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,62</t>
+          <t>-2,65; 0,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,91</t>
+          <t>0,41; 4,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,11</t>
+          <t>-0,92; 2,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,27</t>
+          <t>-2,02; 1,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,79</t>
+          <t>-0,82; 1,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,85</t>
+          <t>-1,57; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,48</t>
+          <t>-1,91; 0,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,32%</t>
+          <t>-49,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,05%</t>
+          <t>-13,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,65%</t>
+          <t>-28,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 9,03</t>
+          <t>-92,1; -3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,49; -18,26</t>
+          <t>-92,77; 1,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,93; 52,7</t>
+          <t>-83,29; 41,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 205,14</t>
+          <t>6,44; 215,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 133,43</t>
+          <t>-23,07; 135,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,9; 53,36</t>
+          <t>-48,56; 66,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 83,85</t>
+          <t>-23,93; 94,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 41,3</t>
+          <t>-46,3; 43,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,27; 25,82</t>
+          <t>-58,06; 13,05</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,47</t>
+          <t>-2,3; 0,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,78</t>
+          <t>-2,12; 0,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,37</t>
+          <t>-1,05; 2,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,89</t>
+          <t>-2,11; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,51</t>
+          <t>-2,8; 2,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,14</t>
+          <t>-1,24; 3,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,29</t>
+          <t>-1,7; 1,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,88</t>
+          <t>-1,85; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,7</t>
+          <t>-0,6; 2,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,04%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 75,28</t>
+          <t>-85,85; 93,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 114,52</t>
+          <t>-82,72; 109,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 137,96</t>
+          <t>-44,71; 269,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 107,97</t>
+          <t>-40,98; 100,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 89,57</t>
+          <t>-48,74; 76,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 108,77</t>
+          <t>-21,75; 114,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 65,6</t>
+          <t>-48,24; 51,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 43,03</t>
+          <t>-49,19; 42,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 73,34</t>
+          <t>-16,5; 97,33</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,81</t>
+          <t>-4,87; -0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,73</t>
+          <t>-4,33; 0,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,74</t>
+          <t>-2,44; 2,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,56</t>
+          <t>-4,36; 2,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,2</t>
+          <t>-6,16; -0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,91</t>
+          <t>-3,05; 2,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,22</t>
+          <t>-3,67; 0,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,46</t>
+          <t>-4,3; -0,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,19</t>
+          <t>-2,04; 1,76</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-95,4; -19,42</t>
+          <t>-95,21; -6,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 72,67</t>
+          <t>-85,84; 34,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 160,14</t>
+          <t>-49,44; 134,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 53,72</t>
+          <t>-48,96; 52,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 15,13</t>
+          <t>-70,86; 1,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 63,81</t>
+          <t>-33,31; 57,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 7,14</t>
+          <t>-58,21; 14,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -10,47</t>
+          <t>-66,76; -7,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 59,62</t>
+          <t>-30,73; 44,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-4,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,38</t>
+          <t>-4,48; 1,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,47</t>
+          <t>-5,2; 0,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,76</t>
+          <t>-3,87; 1,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,16</t>
+          <t>-7,3; 1,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -0,94</t>
+          <t>-8,82; -0,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -2,63</t>
+          <t>-8,04; -0,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1,18</t>
+          <t>-4,68; 0,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -1,26</t>
+          <t>-6,3; -1,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -1,45</t>
+          <t>-5,46; -0,62</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,46%</t>
+          <t>-21,64%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-60,06%</t>
+          <t>-38,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-49,11%</t>
+          <t>-35,07%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 110,2</t>
+          <t>-73,97; 78,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,17; 31,04</t>
+          <t>-86,29; 25,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 75,2</t>
+          <t>-60,8; 78,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 26,88</t>
+          <t>-55,89; 19,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,1; -8,65</t>
+          <t>-67,42; -7,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,55; -30,56</t>
+          <t>-58,95; -7,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 20,73</t>
+          <t>-50,52; 14,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,84; -18,27</t>
+          <t>-67,37; -19,3</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,12; -23,35</t>
+          <t>-56,36; -9,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>-4,41</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 0,05</t>
+          <t>-9,8; 0,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 0,66</t>
+          <t>-9,53; -0,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -0,69</t>
+          <t>-9,36; -0,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,61</t>
+          <t>0,42; 9,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,35</t>
+          <t>-5,0; 3,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,41</t>
+          <t>-0,1; 6,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,57</t>
+          <t>-2,19; 4,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,19</t>
+          <t>-4,97; 1,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,3</t>
+          <t>-3,02; 2,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-55,8%</t>
+          <t>-52,9%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-87,74; 17,85</t>
+          <t>-86,41; 12,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,08; 27,5</t>
+          <t>-77,48; 3,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,05; -6,05</t>
+          <t>-76,08; -6,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,15; 194,34</t>
+          <t>2,21; 194,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 65,21</t>
+          <t>-53,06; 63,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 150,86</t>
+          <t>-1,13; 147,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 77,75</t>
+          <t>-23,1; 78,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,99; 20,96</t>
+          <t>-54,38; 17,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 59,57</t>
+          <t>-28,99; 50,84</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; -0,25</t>
+          <t>-1,58; -0,23</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,68; -0,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,41</t>
+          <t>-0,8; 0,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,74</t>
+          <t>-0,49; 1,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,14</t>
+          <t>-2,24; -0,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-0,98; 0,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,67</t>
+          <t>-0,76; 0,57</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,43</t>
+          <t>-1,66; -0,45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,38</t>
+          <t>-0,64; 0,58</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-2,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-6,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,56%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-61,17; -12,84</t>
+          <t>-61,02; -10,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -15,87</t>
+          <t>-63,34; -16,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 22,73</t>
+          <t>-30,88; 33,52</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 37,26</t>
+          <t>-8,75; 37,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -3,02</t>
+          <t>-37,43; -2,8</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 13,14</t>
+          <t>-16,28; 20,5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 19,7</t>
+          <t>-18,28; 16,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -12,22</t>
+          <t>-39,26; -13,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 11,58</t>
+          <t>-15,26; 16,7</t>
         </is>
       </c>
     </row>
